--- a/api-automacao-mvc-ts/WebhookGLPI.xlsx
+++ b/api-automacao-mvc-ts/WebhookGLPI.xlsx
@@ -1,37 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30317"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A24A70A24DF612FF1F3222C82C2A5EE898596C9B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E00E9EA-847A-4AD8-8145-190C4F7E6BEF}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Plan1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>ID</t>
   </si>
@@ -64,19 +47,28 @@
   </si>
   <si>
     <t>{"id":102,"status":3,"name":"Internet","date":"2026-07-27T17:00:00Z"}</t>
+  </si>
+  <si>
+    <t>Resolvido / Fechado</t>
+  </si>
+  <si>
+    <t>2026-08-13T20:58:31.756Z</t>
+  </si>
+  <si>
+    <t>{"id":111,"status":5,"name":"TESTETESTE","date":"2026-08-13T20:58:31.756Z"}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,8 +111,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:F3">
-  <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Tabela1" displayName="Tabela1" ref="A1:F4" totalsRowShown="1" headerRowCount="1">
+  <autoFilter ref="A1:F4">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -129,12 +121,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titulo"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Status"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Data Criacao"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tempo Espera (Min)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Payload Completo"/>
+    <tableColumn id="1" name="ID" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Titulo" totalsRowFunction="none"/>
+    <tableColumn id="3" name="Status" totalsRowFunction="none"/>
+    <tableColumn id="4" name="Data Criacao" totalsRowFunction="none"/>
+    <tableColumn id="5" name="Tempo Espera (Min)" totalsRowFunction="none"/>
+    <tableColumn id="6" name="Payload Completo" totalsRowFunction="none"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -402,19 +394,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="74.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,7 +426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101</v>
       </c>
@@ -454,7 +446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>102</v>
       </c>
@@ -472,6 +464,26 @@
       </c>
       <c r="F3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
